--- a/Academic Syllabus/Academic Resources.xlsx
+++ b/Academic Syllabus/Academic Resources.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Computer Science and Engineering\Academic Syllabus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Computer-Science-and-Engineering\Academic Syllabus\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{876A9D5C-D9B7-4F0B-830D-D5AC43F4D180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -198,7 +198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -209,21 +209,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -237,7 +231,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -569,13 +562,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>2</v>
       </c>
     </row>
@@ -583,10 +576,10 @@
       <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -594,151 +587,150 @@
       <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B6" s="4"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="14"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="1"/>
-      <c r="C7" s="8"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
-      <c r="C8" s="8"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" s="1"/>
-      <c r="C9" s="8"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="1"/>
-      <c r="C10" s="8"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="1"/>
-      <c r="C11" s="8"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
-      <c r="C12" s="8"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B13" s="1"/>
-      <c r="C13" s="8"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
-      <c r="C14" s="8"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B15" s="1"/>
-      <c r="C15" s="8"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B16" s="1"/>
-      <c r="C16" s="8"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
-      <c r="C17" s="8"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="1"/>
-      <c r="C18" s="8"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="1"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="1"/>
-      <c r="C19" s="8"/>
+      <c r="C19" s="5"/>
       <c r="D19" s="1"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="1"/>
-      <c r="C20" s="8"/>
+      <c r="C20" s="5"/>
       <c r="D20" s="1"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="1"/>
-      <c r="C21" s="8"/>
+      <c r="C21" s="5"/>
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="1"/>
-      <c r="C22" s="8"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="1"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="1"/>
-      <c r="C23" s="8"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="1"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="1"/>
-      <c r="C24" s="8"/>
+      <c r="C24" s="5"/>
       <c r="D24" s="1"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="1"/>
-      <c r="C25" s="8"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="1"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="1"/>
-      <c r="C26" s="8"/>
+      <c r="C26" s="5"/>
       <c r="D26" s="1"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="1"/>
-      <c r="C27" s="8"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="1"/>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="1"/>
-      <c r="C28" s="8"/>
+      <c r="C28" s="5"/>
       <c r="D28" s="1"/>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
-      <c r="C29" s="8"/>
+      <c r="C29" s="5"/>
       <c r="D29" s="1"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="1"/>
-      <c r="C30" s="8"/>
+      <c r="C30" s="5"/>
       <c r="D30" s="1"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C31" s="8"/>
+      <c r="C31" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Academic Syllabus/Academic Resources.xlsx
+++ b/Academic Syllabus/Academic Resources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Computer-Science-and-Engineering\Academic Syllabus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{876A9D5C-D9B7-4F0B-830D-D5AC43F4D180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEF7F4F-14B0-4344-99BE-76A99692BD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{E6170050-33D8-419C-B656-5467068B467E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>SEM</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>Data Structures and Algorithms</t>
+  </si>
+  <si>
+    <t>RESOURCES / LINKS</t>
+  </si>
+  <si>
+    <t>learncpp</t>
   </si>
 </sst>
 </file>
@@ -198,7 +204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -215,26 +221,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -552,109 +572,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1788BE42-54D9-46FF-B406-44985C48683A}">
-  <dimension ref="B2:D31"/>
+  <dimension ref="B2:E31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
     <col min="3" max="3" width="63.6328125" customWidth="1"/>
     <col min="4" max="4" width="113.90625" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" customWidth="1"/>
+    <col min="5" max="5" width="43.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B2" s="7" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E2" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E3" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E4" s="15"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="4">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="1"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="1"/>
       <c r="C7" s="5"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
       <c r="C8" s="5"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="1"/>
       <c r="C9" s="5"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="1"/>
       <c r="C10" s="5"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="1"/>
       <c r="C11" s="5"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
       <c r="C12" s="5"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="1"/>
       <c r="C13" s="5"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
       <c r="C14" s="5"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="1"/>
       <c r="C15" s="5"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="1"/>
       <c r="C16" s="5"/>
       <c r="D16" s="1"/>
@@ -737,6 +765,7 @@
     <hyperlink ref="D4" r:id="rId1" xr:uid="{590B7843-E40C-41C4-B6FF-3BD683DB4103}"/>
     <hyperlink ref="D5" r:id="rId2" xr:uid="{2CCA8F0B-47C4-423A-8CBA-666734443974}"/>
     <hyperlink ref="D3" r:id="rId3" xr:uid="{B56ECC5F-DF50-4765-BD1F-7024ED6C8D6E}"/>
+    <hyperlink ref="E3" r:id="rId4" xr:uid="{7A604E75-8919-413A-9E79-3DF8603794CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
